--- a/cet4/result/28_重生亲情_时光里的父女情深/28_重生亲情_时光里的父女情深_学习版.xlsx
+++ b/cet4/result/28_重生亲情_时光里的父女情深/28_重生亲情_时光里的父女情深_学习版.xlsx
@@ -397,689 +397,577 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D40"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>spring</v>
       </c>
       <c r="B2" t="str">
-        <v>spring</v>
+        <v>/sprɪŋ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D2" t="str">
         <v>春天</v>
       </c>
-      <c r="D2" t="str">
-        <v>spring(春天)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>rear</v>
       </c>
       <c r="B3" t="str">
-        <v>rear</v>
+        <v>/rɪr/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D3" t="str">
         <v>抚养</v>
       </c>
-      <c r="D3" t="str">
-        <v>rear(抚养)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>nine</v>
       </c>
       <c r="B4" t="str">
-        <v>nine</v>
+        <v>/naɪn/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D4" t="str">
         <v>九</v>
       </c>
-      <c r="D4" t="str">
-        <v>nine(九)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>seventeen</v>
       </c>
       <c r="B5" t="str">
-        <v>seventeen</v>
+        <v>/ˌsevnˈtiːn/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D5" t="str">
         <v>十七</v>
       </c>
-      <c r="D5" t="str">
-        <v>seventeen(十七)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>about</v>
       </c>
       <c r="B6" t="str">
-        <v>about</v>
+        <v>/əˈbaʊt/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./adv./prep.</v>
+      </c>
+      <c r="D6" t="str">
         <v>关于</v>
       </c>
-      <c r="D6" t="str">
-        <v>about(关于)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>onion</v>
       </c>
       <c r="B7" t="str">
-        <v>onion</v>
+        <v>/ˈʌnjən/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>洋葱</v>
       </c>
-      <c r="D7" t="str">
-        <v>onion(洋葱)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>principal</v>
       </c>
       <c r="B8" t="str">
-        <v>principal</v>
+        <v>/ˈprɪnsəpl/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>校长</v>
       </c>
-      <c r="D8" t="str">
-        <v>principal(校长)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>blue</v>
       </c>
       <c r="B9" t="str">
-        <v>blue</v>
+        <v>/bluː/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>忧郁的</v>
       </c>
-      <c r="D9" t="str">
-        <v>blue(忧郁的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>danger</v>
       </c>
       <c r="B10" t="str">
-        <v>danger</v>
+        <v>/ˈdeɪndʒər/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>危险</v>
       </c>
-      <c r="D10" t="str">
-        <v>danger(危险)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>bike</v>
       </c>
       <c r="B11" t="str">
-        <v>bike</v>
+        <v>/baɪk/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>自行车</v>
       </c>
-      <c r="D11" t="str">
-        <v>bike(自行车)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>cinema</v>
       </c>
       <c r="B12" t="str">
-        <v>cinema</v>
+        <v>/ˈsɪnəmə/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>电影院</v>
       </c>
-      <c r="D12" t="str">
-        <v>cinema(电影院)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>furious</v>
       </c>
       <c r="B13" t="str">
-        <v>furious</v>
+        <v>/ˈfjʊriəs/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>暴怒的</v>
       </c>
-      <c r="D13" t="str">
-        <v>furious(暴怒的)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>softly</v>
       </c>
       <c r="B14" t="str">
-        <v>softly</v>
+        <v>/ˈsɔːftli/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D14" t="str">
         <v>轻声地</v>
       </c>
-      <c r="D14" t="str">
-        <v>softly(轻声地)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>heavy</v>
       </c>
       <c r="B15" t="str">
-        <v>heavy</v>
+        <v>/ˈhevi/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D15" t="str">
         <v>沉重的</v>
       </c>
-      <c r="D15" t="str">
-        <v>heavy(沉重的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>chain</v>
       </c>
       <c r="B16" t="str">
-        <v>chain</v>
+        <v>/tʃeɪn/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D16" t="str">
         <v>锁链</v>
       </c>
-      <c r="D16" t="str">
-        <v>chain(锁链)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>sacrifice</v>
       </c>
       <c r="B17" t="str">
-        <v>sacrifice</v>
+        <v>/ˈsækrɪfaɪs/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D17" t="str">
         <v>牺牲</v>
       </c>
-      <c r="D17" t="str">
-        <v>sacrifice(牺牲)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>live</v>
       </c>
       <c r="B18" t="str">
-        <v>live</v>
+        <v>/lɪv; laɪv/</v>
       </c>
       <c r="C18" t="str">
+        <v>vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D18" t="str">
         <v>生活</v>
       </c>
-      <c r="D18" t="str">
-        <v>live(生活)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>visit</v>
       </c>
       <c r="B19" t="str">
-        <v>visit</v>
+        <v>/ˈvɪzɪt/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>拜访</v>
       </c>
-      <c r="D19" t="str">
-        <v>visit(拜访)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>chest</v>
       </c>
       <c r="B20" t="str">
-        <v>chest</v>
+        <v>/tʃest/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>箱子</v>
       </c>
-      <c r="D20" t="str">
-        <v>chest(箱子)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>cash</v>
       </c>
       <c r="B21" t="str">
-        <v>cash</v>
+        <v>/kæʃ/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D21" t="str">
         <v>现金</v>
       </c>
-      <c r="D21" t="str">
-        <v>cash(现金)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>economical</v>
       </c>
       <c r="B22" t="str">
-        <v>economical</v>
+        <v>/ˌiːkəˈnɒmɪkl/</v>
       </c>
       <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>节约的</v>
       </c>
-      <c r="D22" t="str">
-        <v>economical(节约的)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>spare</v>
       </c>
       <c r="B23" t="str">
-        <v>spare</v>
+        <v>/sper/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>多余的</v>
       </c>
-      <c r="D23" t="str">
-        <v>spare(多余的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>champion</v>
       </c>
       <c r="B24" t="str">
-        <v>heavy</v>
+        <v>/ˈtʃæmpiən/</v>
       </c>
       <c r="C24" t="str">
-        <v>沉重</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>heavy(沉重)📢</v>
+        <v>冠军</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>dialog</v>
       </c>
       <c r="B25" t="str">
-        <v>champion</v>
+        <v>/ˈdaɪəlɔːɡ/</v>
       </c>
       <c r="C25" t="str">
-        <v>冠军</v>
+        <v>n.</v>
       </c>
       <c r="D25" t="str">
-        <v>champion(冠军)📢</v>
+        <v>对话</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>without</v>
       </c>
       <c r="B26" t="str">
-        <v>dialog</v>
+        <v>/wɪˈðaʊt/</v>
       </c>
       <c r="C26" t="str">
-        <v>对话</v>
+        <v>n./v./adv./prep./conj.</v>
       </c>
       <c r="D26" t="str">
-        <v>dialog(对话)📢</v>
+        <v>没有</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>brush</v>
       </c>
       <c r="B27" t="str">
-        <v>live</v>
+        <v>/brʌʃ/</v>
       </c>
       <c r="C27" t="str">
-        <v>活着</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>live(活着)📢</v>
+        <v>刷</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>player</v>
       </c>
       <c r="B28" t="str">
-        <v>without</v>
+        <v>/ˈpleɪər/</v>
       </c>
       <c r="C28" t="str">
-        <v>没有</v>
+        <v>n.</v>
       </c>
       <c r="D28" t="str">
-        <v>without(没有)📢</v>
+        <v>运动员</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>bird</v>
       </c>
       <c r="B29" t="str">
-        <v>brush</v>
+        <v>/bɜːrd/</v>
       </c>
       <c r="C29" t="str">
-        <v>刷</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>brush(刷)📢</v>
+        <v>鸟</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>summer</v>
       </c>
       <c r="B30" t="str">
-        <v>champion</v>
+        <v>/ˈsʌmər/</v>
       </c>
       <c r="C30" t="str">
-        <v>冠军</v>
+        <v>n./vi./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>champion(冠军)📢</v>
+        <v>夏天</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>recover</v>
       </c>
       <c r="B31" t="str">
-        <v>player</v>
+        <v>/rɪˈkʌvər/</v>
       </c>
       <c r="C31" t="str">
-        <v>运动员</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>player(运动员)📢</v>
+        <v>恢复</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>auxiliary</v>
       </c>
       <c r="B32" t="str">
-        <v>bird</v>
+        <v>/ɔːɡˈzɪliəri/</v>
       </c>
       <c r="C32" t="str">
-        <v>鸟</v>
+        <v>n./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>bird(鸟)📢</v>
+        <v>辅助的</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>gallery</v>
       </c>
       <c r="B33" t="str">
-        <v>summer</v>
+        <v>/ˈɡæləri/</v>
       </c>
       <c r="C33" t="str">
-        <v>夏天</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>summer(夏天)📢</v>
+        <v>画廊</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>mysterious</v>
       </c>
       <c r="B34" t="str">
-        <v>recover</v>
+        <v>/mɪˈstɪriəs/</v>
       </c>
       <c r="C34" t="str">
-        <v>恢复</v>
+        <v>adj.</v>
       </c>
       <c r="D34" t="str">
-        <v>recover(恢复)📢</v>
+        <v>神秘的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>spiritual</v>
       </c>
       <c r="B35" t="str">
-        <v>auxiliary</v>
+        <v>/ˈspɪrɪtʃuəl/</v>
       </c>
       <c r="C35" t="str">
-        <v>辅助的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>auxiliary(辅助的)📢</v>
+        <v>精神的</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>rack</v>
       </c>
       <c r="B36" t="str">
-        <v>gallery</v>
+        <v>/ræk/</v>
       </c>
       <c r="C36" t="str">
-        <v>画廊</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>gallery(画廊)📢</v>
+        <v>架子</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>heroic</v>
       </c>
       <c r="B37" t="str">
-        <v>mysterious</v>
+        <v>/həˈroʊɪk/</v>
       </c>
       <c r="C37" t="str">
-        <v>神秘的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>mysterious(神秘的)📢</v>
+        <v>英雄的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>song</v>
       </c>
       <c r="B38" t="str">
-        <v>spring</v>
+        <v>/sɔŋ/</v>
       </c>
       <c r="C38" t="str">
-        <v>春天</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>spring(春天)📢</v>
+        <v>歌曲</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>brandy</v>
       </c>
       <c r="B39" t="str">
-        <v>spiritual</v>
+        <v>/ˈbrændi/</v>
       </c>
       <c r="C39" t="str">
-        <v>精神的</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>spiritual(精神的)📢</v>
+        <v>白兰地</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>expect</v>
       </c>
       <c r="B40" t="str">
-        <v>rack</v>
+        <v>/ɪkˈspekt/</v>
       </c>
       <c r="C40" t="str">
-        <v>架子</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>rack(架子)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>cash</v>
-      </c>
-      <c r="C41" t="str">
-        <v>现金</v>
-      </c>
-      <c r="D41" t="str">
-        <v>cash(现金)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>heroic</v>
-      </c>
-      <c r="C42" t="str">
-        <v>英雄的</v>
-      </c>
-      <c r="D42" t="str">
-        <v>heroic(英雄的)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>bike</v>
-      </c>
-      <c r="C43" t="str">
-        <v>自行车</v>
-      </c>
-      <c r="D43" t="str">
-        <v>bike(自行车)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>visit</v>
-      </c>
-      <c r="C44" t="str">
-        <v>拜访</v>
-      </c>
-      <c r="D44" t="str">
-        <v>visit(拜访)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>song</v>
-      </c>
-      <c r="C45" t="str">
-        <v>歌曲</v>
-      </c>
-      <c r="D45" t="str">
-        <v>song(歌曲)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>about</v>
-      </c>
-      <c r="C46" t="str">
-        <v>关于</v>
-      </c>
-      <c r="D46" t="str">
-        <v>about(关于)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>brandy</v>
-      </c>
-      <c r="C47" t="str">
-        <v>白兰地</v>
-      </c>
-      <c r="D47" t="str">
-        <v>brandy(白兰地)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>expect</v>
-      </c>
-      <c r="C48" t="str">
         <v>期望</v>
-      </c>
-      <c r="D48" t="str">
-        <v>expect(期望)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D40"/>
   </ignoredErrors>
 </worksheet>
 </file>